--- a/hrm/.plans/elearning-hoc-vien/man-hoc-player/testcase.xlsx
+++ b/hrm/.plans/elearning-hoc-vien/man-hoc-player/testcase.xlsx
@@ -564,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O58"/>
+  <dimension ref="A1:O59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -803,7 +803,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Điều kiện hoàn thành từng bài hiển thị ở dòng 'YC: ...' cạnh trạng thái. Rời tab khi đọc bài viết/tài liệu → dừng đếm giờ (overlay 'Bạn đã tạm rời khỏi bài học'). Bài thi làm trên hệ thống HRM (deep-link).</t>
+          <t>Điều kiện hoàn thành từng bài hiển thị ở dòng 'YC: ...' cạnh trạng thái. Rời tab khi đọc bài viết/tài liệu → dừng đếm giờ (overlay 'Bạn đã tạm rời khỏi bài học'). Bài thi: học viên ngoài làm native trong elearning, nhân viên làm trên HRM (deep-link) — chi tiết ở tài liệu 'Luồng làm bài thi'.</t>
         </is>
       </c>
       <c r="C10" s="4" t="n"/>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="O52" s="14" t="inlineStr"/>
     </row>
-    <row r="53" ht="30" customHeight="1">
+    <row r="53" ht="55" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
           <t>Màn học</t>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>- Modal 📝 'Sẵn sàng làm bài thi!' + 'Làm đề thi' / 'Để sau'</t>
+          <t>- Modal 📝 'Sẵn sàng làm bài thi!'; học viên ngoài 'Bạn đã đủ điều kiện làm bài thi.' / nhân viên '…làm bài thi trên hệ thống Đào tạo (HRM).'; nút 'Làm đề thi'/'Để sau'</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>BR-08 exam prompt</t>
+          <t>BR-08 exam prompt (xem tài liệu 'Luồng làm bài thi')</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr"/>
@@ -3176,17 +3176,17 @@
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>Làm đề thi deep-link HRM</t>
+          <t>Làm đề thi — học viên ngoài (native)</t>
         </is>
       </c>
       <c r="E54" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>Đang mở modal nhắc thi</t>
+          <t>Học viên ngoài, đang mở modal nhắc thi</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>- Chuyển sang hệ thống HRM để làm bài thi (kèm link quay lại)</t>
+          <t>- Mở màn thi native trong elearning (/khoa-hoc/:slug/thi)</t>
         </is>
       </c>
       <c r="J54" s="14" t="inlineStr">
         <is>
-          <t>deep-link exam_link</t>
+          <t>Learner thi native</t>
         </is>
       </c>
       <c r="K54" s="14" t="inlineStr"/>
@@ -3227,95 +3227,95 @@
       </c>
       <c r="O54" s="14" t="inlineStr"/>
     </row>
-    <row r="55" ht="26" customHeight="1">
-      <c r="A55" s="11" t="n"/>
-      <c r="B55" s="11" t="n"/>
-      <c r="C55" s="12" t="inlineStr">
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Màn học</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>HOÀN THÀNH KHÓA &amp; BÀI THI</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>TC_07.005</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Làm đề thi — nhân viên (HRM)</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Nhân viên, đang mở modal nhắc thi</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>1. Bấm 'Làm đề thi'</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>- Chuyển sang hệ thống HRM để làm bài thi (kèm link quay lại)</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>Employee deep-link HRM</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr"/>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56" ht="26" customHeight="1">
+      <c r="A56" s="11" t="n"/>
+      <c r="B56" s="11" t="n"/>
+      <c r="C56" s="12" t="inlineStr">
         <is>
           <t>VIII. HỌC TRONG LỘ TRÌNH (?lp=)</t>
         </is>
       </c>
-      <c r="D55" s="4" t="n"/>
-      <c r="E55" s="4" t="n"/>
-      <c r="F55" s="4" t="n"/>
-      <c r="G55" s="4" t="n"/>
-      <c r="H55" s="4" t="n"/>
-      <c r="I55" s="4" t="n"/>
-      <c r="J55" s="4" t="n"/>
-      <c r="K55" s="4" t="n"/>
-      <c r="L55" s="4" t="n"/>
-      <c r="M55" s="4" t="n"/>
-      <c r="N55" s="4" t="n"/>
-      <c r="O55" s="5" t="n"/>
-    </row>
-    <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>Màn học</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>HỌC TRONG LỘ TRÌNH (?lp=)</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>TC_08.001</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>Hoàn thành khóa còn khóa tiếp theo</t>
-        </is>
-      </c>
-      <c r="E56" s="13" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="inlineStr">
-        <is>
-          <t>Đang học 1 khóa trong lộ trình còn khóa sau chưa xong</t>
-        </is>
-      </c>
-      <c r="G56" s="3" t="inlineStr">
-        <is>
-          <t>1. Hoàn thành khóa hiện tại</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I56" s="3" t="inlineStr">
-        <is>
-          <t>- Modal 'Hoàn thành khoá học!' + nút 'Học khoá tiếp theo: {tên}' + 'Quay lại lộ trình'</t>
-        </is>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>?lp mode</t>
-        </is>
-      </c>
-      <c r="K56" s="3" t="inlineStr"/>
-      <c r="L56" s="3" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M56" s="3" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N56" s="3" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="O56" s="3" t="inlineStr"/>
+      <c r="D56" s="4" t="n"/>
+      <c r="E56" s="4" t="n"/>
+      <c r="F56" s="4" t="n"/>
+      <c r="G56" s="4" t="n"/>
+      <c r="H56" s="4" t="n"/>
+      <c r="I56" s="4" t="n"/>
+      <c r="J56" s="4" t="n"/>
+      <c r="K56" s="4" t="n"/>
+      <c r="L56" s="4" t="n"/>
+      <c r="M56" s="4" t="n"/>
+      <c r="N56" s="4" t="n"/>
+      <c r="O56" s="5" t="n"/>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="14" t="inlineStr">
@@ -3330,27 +3330,27 @@
       </c>
       <c r="C57" s="14" t="inlineStr">
         <is>
-          <t>TC_08.002</t>
+          <t>TC_08.001</t>
         </is>
       </c>
       <c r="D57" s="14" t="inlineStr">
         <is>
-          <t>Học sang khóa tiếp theo giữ ngữ cảnh</t>
+          <t>Hoàn thành khóa còn khóa tiếp theo</t>
         </is>
       </c>
       <c r="E57" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F57" s="14" t="inlineStr">
         <is>
-          <t>Đang mở modal có nút 'Học khoá tiếp theo'</t>
+          <t>Đang học 1 khóa trong lộ trình còn khóa sau chưa xong</t>
         </is>
       </c>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>1. Bấm 'Học khoá tiếp theo: {tên}'</t>
+          <t>1. Hoàn thành khóa hiện tại</t>
         </is>
       </c>
       <c r="H57" s="14" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I57" s="14" t="inlineStr">
         <is>
-          <t>- Chuyển sang màn học khóa kế, vẫn giữ ngữ cảnh lộ trình (nút quay lại là 'Lộ trình')</t>
+          <t>- Modal 'Hoàn thành khoá học!' + nút 'Học khoá tiếp theo: {tên}' + 'Quay lại lộ trình'</t>
         </is>
       </c>
       <c r="J57" s="14" t="inlineStr">
         <is>
-          <t>giữ query ?lp</t>
+          <t>?lp mode</t>
         </is>
       </c>
       <c r="K57" s="14" t="inlineStr"/>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O57" s="14" t="inlineStr"/>
     </row>
-    <row r="58" ht="37" customHeight="1">
+    <row r="58" ht="30" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
           <t>Màn học</t>
@@ -3399,27 +3399,27 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>TC_08.003</t>
+          <t>TC_08.002</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Hoàn thành cả lộ trình</t>
+          <t>Học sang khóa tiếp theo giữ ngữ cảnh</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Hoàn thành khóa cuối trong lộ trình</t>
+          <t>Đang mở modal có nút 'Học khoá tiếp theo'</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>1. Hoàn thành khóa cuối</t>
+          <t>1. Bấm 'Học khoá tiếp theo: {tên}'</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
@@ -3429,12 +3429,12 @@
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>- Modal 'Chúc mừng! Bạn đã hoàn thành lộ trình' + 'Xem chứng chỉ lộ trình' (nếu bật) + 'Khám phá lộ trình khác'</t>
+          <t>- Chuyển sang màn học khóa kế, vẫn giữ ngữ cảnh lộ trình (nút quay lại là 'Lộ trình')</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>lpComplete</t>
+          <t>giữ query ?lp</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr"/>
@@ -3454,6 +3454,75 @@
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59" ht="37" customHeight="1">
+      <c r="A59" s="14" t="inlineStr">
+        <is>
+          <t>Màn học</t>
+        </is>
+      </c>
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t>HỌC TRONG LỘ TRÌNH (?lp=)</t>
+        </is>
+      </c>
+      <c r="C59" s="14" t="inlineStr">
+        <is>
+          <t>TC_08.003</t>
+        </is>
+      </c>
+      <c r="D59" s="14" t="inlineStr">
+        <is>
+          <t>Hoàn thành cả lộ trình</t>
+        </is>
+      </c>
+      <c r="E59" s="15" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F59" s="14" t="inlineStr">
+        <is>
+          <t>Hoàn thành khóa cuối trong lộ trình</t>
+        </is>
+      </c>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>1. Hoàn thành khóa cuối</t>
+        </is>
+      </c>
+      <c r="H59" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I59" s="14" t="inlineStr">
+        <is>
+          <t>- Modal 'Chúc mừng! Bạn đã hoàn thành lộ trình' + 'Xem chứng chỉ lộ trình' (nếu bật) + 'Khám phá lộ trình khác'</t>
+        </is>
+      </c>
+      <c r="J59" s="14" t="inlineStr">
+        <is>
+          <t>lpComplete</t>
+        </is>
+      </c>
+      <c r="K59" s="14" t="inlineStr"/>
+      <c r="L59" s="14" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M59" s="14" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N59" s="14" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="O59" s="14" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -3480,16 +3549,16 @@
     <mergeCell ref="L15:O15"/>
     <mergeCell ref="F11:H11"/>
     <mergeCell ref="I15:K15"/>
-    <mergeCell ref="C55:O55"/>
     <mergeCell ref="B9:O9"/>
     <mergeCell ref="I11:K11"/>
     <mergeCell ref="C50:O50"/>
     <mergeCell ref="L14:O14"/>
     <mergeCell ref="B6:O6"/>
+    <mergeCell ref="C56:O56"/>
     <mergeCell ref="B5:O5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="L18:N159" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L18:N160" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Passed,Failed,Pending,Not Executed"</formula1>
     </dataValidation>
   </dataValidations>
